--- a/artfynd/A 58570-2020 artfynd.xlsx
+++ b/artfynd/A 58570-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 58570-2020 artfynd.xlsx
+++ b/artfynd/A 58570-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -915,6 +915,339 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>122031791</v>
+      </c>
+      <c r="B4" t="n">
+        <v>78365</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Nornäs, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>408365</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6810012</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-11-07</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-11-07</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>122031625</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79218</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Nornäs, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>408367</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6810012</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-11-07</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-11-07</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>122031482</v>
+      </c>
+      <c r="B6" t="n">
+        <v>92018</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Nornäs, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>408722</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6809931</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-11-07</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-11-07</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 58570-2020 artfynd.xlsx
+++ b/artfynd/A 58570-2020 artfynd.xlsx
@@ -917,10 +917,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122031791</v>
+        <v>122031625</v>
       </c>
       <c r="B4" t="n">
-        <v>78365</v>
+        <v>79220</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -933,21 +933,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -961,7 +961,7 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>408365</v>
+        <v>408367</v>
       </c>
       <c r="R4" t="n">
         <v>6810012</v>
@@ -1028,10 +1028,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122031625</v>
+        <v>122031791</v>
       </c>
       <c r="B5" t="n">
-        <v>79218</v>
+        <v>78367</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1044,21 +1044,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1072,7 +1072,7 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>408367</v>
+        <v>408365</v>
       </c>
       <c r="R5" t="n">
         <v>6810012</v>
@@ -1142,7 +1142,7 @@
         <v>122031482</v>
       </c>
       <c r="B6" t="n">
-        <v>92018</v>
+        <v>92020</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 58570-2020 artfynd.xlsx
+++ b/artfynd/A 58570-2020 artfynd.xlsx
@@ -917,10 +917,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122031625</v>
+        <v>122031791</v>
       </c>
       <c r="B4" t="n">
-        <v>79220</v>
+        <v>78368</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -933,21 +933,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -961,7 +961,7 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>408367</v>
+        <v>408365</v>
       </c>
       <c r="R4" t="n">
         <v>6810012</v>
@@ -1028,10 +1028,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122031791</v>
+        <v>122031625</v>
       </c>
       <c r="B5" t="n">
-        <v>78367</v>
+        <v>79221</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1044,21 +1044,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1072,7 +1072,7 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>408365</v>
+        <v>408367</v>
       </c>
       <c r="R5" t="n">
         <v>6810012</v>
@@ -1142,7 +1142,7 @@
         <v>122031482</v>
       </c>
       <c r="B6" t="n">
-        <v>92020</v>
+        <v>92021</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 58570-2020 artfynd.xlsx
+++ b/artfynd/A 58570-2020 artfynd.xlsx
@@ -920,7 +920,7 @@
         <v>122031791</v>
       </c>
       <c r="B4" t="n">
-        <v>78368</v>
+        <v>78375</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>122031625</v>
       </c>
       <c r="B5" t="n">
-        <v>79221</v>
+        <v>79228</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
         <v>122031482</v>
       </c>
       <c r="B6" t="n">
-        <v>92021</v>
+        <v>92030</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 58570-2020 artfynd.xlsx
+++ b/artfynd/A 58570-2020 artfynd.xlsx
@@ -920,7 +920,7 @@
         <v>122031791</v>
       </c>
       <c r="B4" t="n">
-        <v>78381</v>
+        <v>78382</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>122031625</v>
       </c>
       <c r="B5" t="n">
-        <v>79234</v>
+        <v>79235</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
         <v>122031482</v>
       </c>
       <c r="B6" t="n">
-        <v>92055</v>
+        <v>92065</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 58570-2020 artfynd.xlsx
+++ b/artfynd/A 58570-2020 artfynd.xlsx
@@ -917,10 +917,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122031791</v>
+        <v>122031625</v>
       </c>
       <c r="B4" t="n">
-        <v>78382</v>
+        <v>79240</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -933,21 +933,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -961,7 +961,7 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>408365</v>
+        <v>408367</v>
       </c>
       <c r="R4" t="n">
         <v>6810012</v>
@@ -1028,10 +1028,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122031625</v>
+        <v>122031791</v>
       </c>
       <c r="B5" t="n">
-        <v>79235</v>
+        <v>78387</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1044,21 +1044,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1072,7 +1072,7 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>408367</v>
+        <v>408365</v>
       </c>
       <c r="R5" t="n">
         <v>6810012</v>
@@ -1142,7 +1142,7 @@
         <v>122031482</v>
       </c>
       <c r="B6" t="n">
-        <v>92065</v>
+        <v>92077</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 58570-2020 artfynd.xlsx
+++ b/artfynd/A 58570-2020 artfynd.xlsx
@@ -1142,7 +1142,7 @@
         <v>122031482</v>
       </c>
       <c r="B6" t="n">
-        <v>92077</v>
+        <v>92082</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
